--- a/utils/monday_sprint_sprint_2026-05.xlsx
+++ b/utils/monday_sprint_sprint_2026-05.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="810" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="809" uniqueCount="240">
   <si>
     <t>Ticket</t>
   </si>
@@ -102,7 +102,7 @@
     <t>16/12/2025</t>
   </si>
   <si>
-    <t>02/03/2026</t>
+    <t>25/02/2026</t>
   </si>
   <si>
     <t>Semana 3</t>
@@ -171,7 +171,7 @@
     <t>30/05/2025</t>
   </si>
   <si>
-    <t>14/03/2026</t>
+    <t>09/03/2026</t>
   </si>
   <si>
     <t>Semana 5</t>
@@ -198,7 +198,7 @@
     <t>19/11/2025</t>
   </si>
   <si>
-    <t>24/03/2026</t>
+    <t>19/03/2026</t>
   </si>
   <si>
     <t>Novembro</t>
@@ -246,7 +246,7 @@
     <t>02/12/2025</t>
   </si>
   <si>
-    <t>25/02/2026</t>
+    <t>20/02/2026</t>
   </si>
   <si>
     <t>35367</t>
@@ -264,6 +264,9 @@
     <t>20/11/2025</t>
   </si>
   <si>
+    <t>19/05/2026</t>
+  </si>
+  <si>
     <t>35806</t>
   </si>
   <si>
@@ -279,6 +282,15 @@
     <t>Alteração aplicação Usinagem IROG</t>
   </si>
   <si>
+    <t>Boa tarde Felipe, Conforme conversamos via Teams, favor alterar base de dados para a aplicação Indicadores Usinagem, para a mesma base da Usinagem IROG ou abrir uma nova pasta na aplicação e criar os mesmos gráficos. Grato,</t>
+  </si>
+  <si>
+    <t>Caio Henrique Vicente Bento</t>
+  </si>
+  <si>
+    <t>15/12/2025</t>
+  </si>
+  <si>
     <t>27502</t>
   </si>
   <si>
@@ -300,7 +312,7 @@
     <t>Bom dia, Estou em contato com o Analista Felipe para fazer as correções de calculo de MTBF. A fórmula precisa ser: ex: -Filtro de 1 mes ativo -20 horas de parada durante esse mes inteiro -20 paradas no mês seria todos os dias que aquela maquina parou, vamos supor que seja 24h por dia. 24x30 = 720 ho</t>
   </si>
   <si>
-    <t>01/03/2026</t>
+    <t>24/02/2026</t>
   </si>
   <si>
     <t>Homologação</t>
@@ -357,7 +369,7 @@
     <t>20/12/2025</t>
   </si>
   <si>
-    <t>15/04/2026</t>
+    <t>10/04/2026</t>
   </si>
   <si>
     <t>34171</t>
@@ -390,7 +402,7 @@
     <t>07/01/2026</t>
   </si>
   <si>
-    <t>04/03/2026</t>
+    <t>27/02/2026</t>
   </si>
   <si>
     <t>Implantação</t>
@@ -519,7 +531,7 @@
     <t>Eduardo Basso Pinto</t>
   </si>
   <si>
-    <t>25/03/2026</t>
+    <t>20/03/2026</t>
   </si>
   <si>
     <t>35765</t>
@@ -588,7 +600,7 @@
     <t>25/11/2025</t>
   </si>
   <si>
-    <t>11/03/2026</t>
+    <t>06/03/2026</t>
   </si>
   <si>
     <t>32150</t>
@@ -1801,7 +1813,7 @@
         <v>82</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>17</v>
+        <v>83</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>20</v>
@@ -1815,22 +1827,22 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>19</v>
@@ -1859,7 +1871,7 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>15</v>
@@ -1868,42 +1880,42 @@
         <v>16</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>49</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>17</v>
+        <v>91</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>17</v>
+        <v>83</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>20</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>15</v>
@@ -1915,10 +1927,10 @@
         <v>17</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>19</v>
@@ -1947,7 +1959,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>15</v>
@@ -1959,10 +1971,10 @@
         <v>17</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>19</v>
@@ -1991,7 +2003,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>15</v>
@@ -2003,10 +2015,10 @@
         <v>23</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>19</v>
@@ -2021,10 +2033,10 @@
         <v>28</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M20" s="2" t="s">
         <v>30</v>
@@ -2035,7 +2047,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>15</v>
@@ -2047,25 +2059,25 @@
         <v>23</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>27</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>17</v>
+        <v>83</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>20</v>
@@ -2074,12 +2086,12 @@
         <v>37</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>15</v>
@@ -2091,10 +2103,10 @@
         <v>17</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>19</v>
@@ -2123,7 +2135,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>15</v>
@@ -2135,10 +2147,10 @@
         <v>17</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>19</v>
@@ -2167,7 +2179,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>15</v>
@@ -2179,10 +2191,10 @@
         <v>17</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>19</v>
@@ -2211,7 +2223,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>15</v>
@@ -2223,28 +2235,28 @@
         <v>23</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>27</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M25" s="2" t="s">
         <v>30</v>
@@ -2255,7 +2267,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>15</v>
@@ -2267,10 +2279,10 @@
         <v>17</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>19</v>
@@ -2299,7 +2311,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>15</v>
@@ -2311,10 +2323,10 @@
         <v>17</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>19</v>
@@ -2343,7 +2355,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>15</v>
@@ -2355,39 +2367,39 @@
         <v>23</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="M28" s="2" t="s">
         <v>70</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>15</v>
@@ -2399,10 +2411,10 @@
         <v>17</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>19</v>
@@ -2431,7 +2443,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>15</v>
@@ -2443,10 +2455,10 @@
         <v>17</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>19</v>
@@ -2475,22 +2487,22 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>19</v>
@@ -2519,7 +2531,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>15</v>
@@ -2531,25 +2543,25 @@
         <v>23</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>49</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>17</v>
+        <v>83</v>
       </c>
       <c r="L32" s="2" t="s">
         <v>20</v>
@@ -2558,12 +2570,12 @@
         <v>53</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>15</v>
@@ -2575,10 +2587,10 @@
         <v>17</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>49</v>
@@ -2607,7 +2619,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>15</v>
@@ -2619,10 +2631,10 @@
         <v>17</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>19</v>
@@ -2651,7 +2663,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>15</v>
@@ -2663,10 +2675,10 @@
         <v>17</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>19</v>
@@ -2695,22 +2707,22 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>19</v>
@@ -2719,13 +2731,13 @@
         <v>35</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="L36" s="2" t="s">
         <v>20</v>
@@ -2734,12 +2746,12 @@
         <v>37</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>15</v>
@@ -2751,25 +2763,25 @@
         <v>23</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="I37" s="2" t="s">
         <v>27</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="L37" s="2" t="s">
         <v>20</v>
@@ -2783,7 +2795,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>15</v>
@@ -2795,22 +2807,22 @@
         <v>23</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="K38" s="2" t="s">
         <v>52</v>
@@ -2827,7 +2839,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>15</v>
@@ -2839,10 +2851,10 @@
         <v>17</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>19</v>
@@ -2871,7 +2883,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>15</v>
@@ -2883,16 +2895,16 @@
         <v>23</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>27</v>
@@ -2901,7 +2913,7 @@
         <v>69</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="L40" s="2" t="s">
         <v>20</v>
@@ -2915,7 +2927,7 @@
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>15</v>
@@ -2927,10 +2939,10 @@
         <v>17</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>19</v>
@@ -2959,7 +2971,7 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>15</v>
@@ -2971,10 +2983,10 @@
         <v>17</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>19</v>
@@ -3003,7 +3015,7 @@
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>15</v>
@@ -3015,10 +3027,10 @@
         <v>17</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>19</v>
@@ -3047,7 +3059,7 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>15</v>
@@ -3059,10 +3071,10 @@
         <v>17</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>19</v>
@@ -3091,19 +3103,19 @@
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>17</v>
@@ -3112,13 +3124,13 @@
         <v>49</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="I45" s="2" t="s">
         <v>27</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="K45" s="2" t="s">
         <v>17</v>
@@ -3130,24 +3142,24 @@
         <v>21</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>17</v>
@@ -3156,13 +3168,13 @@
         <v>49</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>27</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="K46" s="2" t="s">
         <v>17</v>
@@ -3174,12 +3186,12 @@
         <v>21</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>15</v>
@@ -3191,10 +3203,10 @@
         <v>17</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>19</v>
@@ -3223,7 +3235,7 @@
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>15</v>
@@ -3235,25 +3247,25 @@
         <v>23</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="L48" s="2" t="s">
         <v>20</v>
@@ -3267,7 +3279,7 @@
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>15</v>
@@ -3279,39 +3291,39 @@
         <v>23</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>17</v>
+        <v>83</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="M49" s="2" t="s">
         <v>70</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>15</v>
@@ -3323,39 +3335,39 @@
         <v>23</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>17</v>
+        <v>83</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M50" s="2" t="s">
         <v>53</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>15</v>
@@ -3367,54 +3379,54 @@
         <v>23</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>49</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="M51" s="2" t="s">
         <v>21</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>19</v>
@@ -3432,7 +3444,7 @@
         <v>17</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="M52" s="2" t="s">
         <v>21</v>
@@ -3454,23 +3466,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B2" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D2" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="E2" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -3478,16 +3490,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -3506,7 +3518,7 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -3519,7 +3531,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="K23">
         <v>4</v>
@@ -3527,7 +3539,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -3558,12 +3570,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="B2">
         <v>51</v>
@@ -3587,25 +3599,25 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -3622,13 +3634,13 @@
         <v>43</v>
       </c>
       <c r="G10" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -3643,12 +3655,12 @@
         <v>70</v>
       </c>
       <c r="Q10">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E11">
         <v>4</v>
@@ -3660,13 +3672,13 @@
         <v>8</v>
       </c>
       <c r="J11" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="K11">
         <v>51</v>
       </c>
       <c r="M11" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="N11">
         <v>0</v>
@@ -3675,7 +3687,7 @@
         <v>37</v>
       </c>
       <c r="Q11">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="4:17" x14ac:dyDescent="0.25">
@@ -3692,7 +3704,7 @@
         <v>42</v>
       </c>
       <c r="M12" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="N12">
         <v>0</v>
@@ -3701,24 +3713,24 @@
         <v>30</v>
       </c>
       <c r="Q12">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D13" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E13">
         <v>2</v>
       </c>
       <c r="G13" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="H13">
         <v>1</v>
       </c>
       <c r="M13" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="N13">
         <v>0</v>
@@ -3727,32 +3739,26 @@
         <v>21</v>
       </c>
       <c r="Q13">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="14" spans="7:17" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="M14" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="N14">
         <v>4</v>
       </c>
-      <c r="P14" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q14">
-        <v>1</v>
-      </c>
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="N15">
         <v>3</v>
@@ -3760,7 +3766,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -3768,7 +3774,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -3776,7 +3782,7 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
@@ -3787,7 +3793,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -3795,35 +3801,35 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F21" s="2">
-        <v>715</v>
+        <v>709</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>134</v>
+        <v>201</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F22" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>135</v>
+        <v>202</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>197</v>
+        <v>138</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>15</v>
@@ -3832,26 +3838,26 @@
         <v>458</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>198</v>
+        <v>139</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F24" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>15</v>
@@ -3860,35 +3866,35 @@
         <v>332</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F26" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F27" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3899,7 +3905,7 @@
         <v>15</v>
       </c>
       <c r="F28" s="2">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>47</v>
@@ -3913,7 +3919,7 @@
         <v>15</v>
       </c>
       <c r="F29" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>33</v>
@@ -3927,7 +3933,7 @@
         <v>15</v>
       </c>
       <c r="F30" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>79</v>

--- a/utils/monday_sprint_sprint_2026-05.xlsx
+++ b/utils/monday_sprint_sprint_2026-05.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="868" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="871" uniqueCount="218">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -60,7 +60,7 @@
     <t>Mês</t>
   </si>
   <si>
-    <t>35890</t>
+    <t>11116112144</t>
   </si>
   <si>
     <t>Setor não informado</t>
@@ -87,450 +87,453 @@
     <t>27/01/2026</t>
   </si>
   <si>
+    <t>12/01/2026</t>
+  </si>
+  <si>
+    <t>Feito</t>
+  </si>
+  <si>
+    <t>Sim</t>
+  </si>
+  <si>
+    <t>Semana 4</t>
+  </si>
+  <si>
+    <t>Janeiro</t>
+  </si>
+  <si>
+    <t>11116094978</t>
+  </si>
+  <si>
+    <t>Indicadores Diários - IROG</t>
+  </si>
+  <si>
+    <t>13/01/2026</t>
+  </si>
+  <si>
+    <t>11116111577</t>
+  </si>
+  <si>
+    <t>Sistema de Embalagens - Relatório Requisição Embalagem por Sequência</t>
+  </si>
+  <si>
+    <t>11116112110</t>
+  </si>
+  <si>
+    <t>Romaneio</t>
+  </si>
+  <si>
+    <t>11116111609</t>
+  </si>
+  <si>
+    <t>Solicitação de atualização de integração no sistema de embalagens</t>
+  </si>
+  <si>
+    <t>18/01/2026</t>
+  </si>
+  <si>
+    <t>11116116263</t>
+  </si>
+  <si>
+    <t>Melhoria do sistema de cadastro</t>
+  </si>
+  <si>
+    <t>14/01/2026</t>
+  </si>
+  <si>
+    <t>11116111576</t>
+  </si>
+  <si>
+    <t>Projeto</t>
+  </si>
+  <si>
+    <t>Ajustes Dalca e Lianco</t>
+  </si>
+  <si>
+    <t>Alta</t>
+  </si>
+  <si>
+    <t>11116104206</t>
+  </si>
+  <si>
+    <t>Melhoria sistema de manutenção - Reunião</t>
+  </si>
+  <si>
+    <t>35353</t>
+  </si>
+  <si>
+    <t>Excelência Operacional</t>
+  </si>
+  <si>
+    <t>Solicitação de serviço</t>
+  </si>
+  <si>
+    <t>Criação do IROG do Tratamento Térmico</t>
+  </si>
+  <si>
+    <t>Bom dia Srs., Precisamos que seja criado uma aba para visualização do IROG do Tratamento Térmico. Incluir o ícone nessa aba: Link do apontamento do Tratamento Térmico: https://mes.altona.com.br/KB_EAA_TOTONETFrameworkOracle/wtt000.aspx Lançar os dados que estão sendo gerados nesse apontamento para a</t>
+  </si>
+  <si>
+    <t>Gabriel Lucas Kertichka</t>
+  </si>
+  <si>
+    <t>Sistemas</t>
+  </si>
+  <si>
+    <t>19/03/2026</t>
+  </si>
+  <si>
+    <t>Não</t>
+  </si>
+  <si>
+    <t>11116115467</t>
+  </si>
+  <si>
+    <t>Indicador Cobertura de Estoques</t>
+  </si>
+  <si>
+    <t>11116111994</t>
+  </si>
+  <si>
+    <t>Log de método dentro do sistema de baixa de preventivas e planejamento e programação</t>
+  </si>
+  <si>
+    <t>35665</t>
+  </si>
+  <si>
+    <t>Fundição</t>
+  </si>
+  <si>
+    <t>APONTAMNETO LINHAS UPR - ADEQUAÇÕES PARA LINHA FHASE FOUR</t>
+  </si>
+  <si>
+    <t>Boa tarde, Adequações a serem feitas no sistema eletrônico UPR para linha Fhase Four. * Retirada da opção lado mesa A / B (não necessário, a linha não utiliza o sistema de mesa redonda). * Habilitar a opção de abrir parada sem sequência (habilitar essa função para todas as linhas). Obs; Durante os t</t>
+  </si>
+  <si>
+    <t>Douglas Garcia</t>
+  </si>
+  <si>
+    <t>01/06/2026</t>
+  </si>
+  <si>
+    <t>11116115318</t>
+  </si>
+  <si>
+    <t>Implementação de Índice de Qualidade de Manutenção</t>
+  </si>
+  <si>
+    <t>35367</t>
+  </si>
+  <si>
+    <t>Mecânica</t>
+  </si>
+  <si>
+    <t>Indicadores MTTR e MDT</t>
+  </si>
+  <si>
+    <t>Bom dia, Quero solicitar, se possível, fazer uma alteração no sistema de manutenção para que ele possa calcular o MTTR e o MDT separados. Todavia, sabendo que ambos se complementam porque o MDT calcula o tempo total da máquina parada que seria quando o operador abre a O.S e coloca a máquina em manut</t>
+  </si>
+  <si>
+    <t>Glória Danielly Lima Rodrigues</t>
+  </si>
+  <si>
+    <t>19/05/2026</t>
+  </si>
+  <si>
+    <t>11116105012</t>
+  </si>
+  <si>
+    <t>Correção</t>
+  </si>
+  <si>
+    <t>ALTERAÇÃO NA TELA DE LANÇAMENTO DE CTE</t>
+  </si>
+  <si>
+    <t>15/01/2026</t>
+  </si>
+  <si>
+    <t>35729</t>
+  </si>
+  <si>
+    <t>Usinagem</t>
+  </si>
+  <si>
+    <t>Alteração aplicação Usinagem IROG</t>
+  </si>
+  <si>
+    <t>Boa tarde Felipe, Conforme conversamos via Teams, favor alterar base de dados para a aplicação Indicadores Usinagem, para a mesma base da Usinagem IROG ou abrir uma nova pasta na aplicação e criar os mesmos gráficos. Grato,</t>
+  </si>
+  <si>
+    <t>Caio Henrique Vicente Bento</t>
+  </si>
+  <si>
+    <t>11116111315</t>
+  </si>
+  <si>
+    <t>Cartão de Vazamento</t>
+  </si>
+  <si>
+    <t>19/01/2026</t>
+  </si>
+  <si>
+    <t>11116115573</t>
+  </si>
+  <si>
+    <t>Melhorias sistema de corridas</t>
+  </si>
+  <si>
+    <t>11116115347</t>
+  </si>
+  <si>
+    <t>Correção Calculo MTBF</t>
+  </si>
+  <si>
+    <t>26/01/2026</t>
+  </si>
+  <si>
+    <t>Homologação</t>
+  </si>
+  <si>
+    <t>30012</t>
+  </si>
+  <si>
+    <t>PCP</t>
+  </si>
+  <si>
+    <t>Melhorias APS</t>
+  </si>
+  <si>
+    <t>Objetivo: alimentar dados mestres nas tabelas do APS 8-9. Levantamento de informações para a especificação funcional do projeto. ( TI especificação de interface inicial) REALIZADO @Edson João Hammermeister por favor indicar tempo para essa atividade. Atenciosamente, De: João Pedro Beccon Enviada em:</t>
+  </si>
+  <si>
+    <t>João Pedro Beccon</t>
+  </si>
+  <si>
+    <t>11116116010</t>
+  </si>
+  <si>
+    <t>Atalho Corridas</t>
+  </si>
+  <si>
+    <t>11116094887</t>
+  </si>
+  <si>
+    <t>SISTEMÁTICA REABERTURA DE ANÁLISE CRÍTICA</t>
+  </si>
+  <si>
+    <t>22/01/2026</t>
+  </si>
+  <si>
+    <t>11116115115</t>
+  </si>
+  <si>
+    <t>Impressão de Solicitações</t>
+  </si>
+  <si>
+    <t>35808</t>
+  </si>
+  <si>
+    <t>Unificação de dados das aplicações de "Apontamento solda" x "Retrabalho Rebarbação</t>
+  </si>
+  <si>
+    <t>Bom dia! Percebi que não houve saída para abertura de um chamado sobre esta demanda "Unificação de dados das aplicações de "Apontamento solda" x "Retrabalho Rebarbação - item solda"" solicitada durante reuniões de meados de agosto e setembro/2025 conforme meus registros aqui. Solicito por aqui, entã</t>
+  </si>
+  <si>
+    <t>Fernanda da Costa Rodrigues</t>
+  </si>
+  <si>
+    <t>10/04/2026</t>
+  </si>
+  <si>
+    <t>11116104599</t>
+  </si>
+  <si>
+    <t>Contagem Proformas</t>
+  </si>
+  <si>
+    <t>11116094605</t>
+  </si>
+  <si>
+    <t>Integração do mapeamento digital com sistema do PCP</t>
+  </si>
+  <si>
+    <t>11116111536</t>
+  </si>
+  <si>
+    <t>Colocar campo de etiqueta no inventário</t>
+  </si>
+  <si>
+    <t>Implantação</t>
+  </si>
+  <si>
+    <t>11116094862</t>
+  </si>
+  <si>
+    <t>LOG DE ALTERAÇÃO DE CPP</t>
+  </si>
+  <si>
+    <t>11116111986</t>
+  </si>
+  <si>
+    <t>Altona || Estoque IMOB 39551 - Entradas + Consumo Diferente do Saldo</t>
+  </si>
+  <si>
+    <t>11116121466</t>
+  </si>
+  <si>
+    <t>FTF x Realizado</t>
+  </si>
+  <si>
+    <t>29853</t>
+  </si>
+  <si>
+    <t>Logística</t>
+  </si>
+  <si>
+    <t>WMS - Sistema de Picking - Distribuição de Estoque em carteira</t>
+  </si>
+  <si>
+    <t>Boa tarde Conforme conversamos, precisamos de um sistema dentro do WMS que faça a distribuição em tempo real do saldo do Estoque com a carteira. Conforme é realizado o faturamento, a carteira seja atualizada em tempo real, bem como a entrada e estorno do material. O sistema deve fornecer um relatóri</t>
+  </si>
+  <si>
+    <t>Djalma Machado</t>
+  </si>
+  <si>
+    <t>ADH</t>
+  </si>
+  <si>
+    <t>11116104632</t>
+  </si>
+  <si>
+    <t>Gestão de Pacotes - Ação Melhoria Sistema de Materiais x Supervisório</t>
+  </si>
+  <si>
+    <t>11116111656</t>
+  </si>
+  <si>
+    <t>ACESSO A TELA DE EXCLUSÃO DE SETOR EM VÁRIAS SEQUÊNCIAS</t>
+  </si>
+  <si>
+    <t>11116111838</t>
+  </si>
+  <si>
+    <t>Erro no cadastro do tempo padrão</t>
+  </si>
+  <si>
+    <t>11116111791</t>
+  </si>
+  <si>
+    <t>Incluir consistência para não permitir data/hora inicial em branco no apontamento</t>
+  </si>
+  <si>
+    <t>34720</t>
+  </si>
+  <si>
+    <t>Almoxarifado</t>
+  </si>
+  <si>
+    <t>Solicitação de Implementação – Coleta de Assinatura Digital para Declaração de Recebimento - Apresentação Sistema</t>
+  </si>
+  <si>
+    <t>Boa tarde Gostaria de solicitar a implementação de uma funcionalidade para coleta de assinatura digital referente à Declaração de Recebimento de materiais. Contexto do Processo Atual Hoje, ao receber o romaneio/cópia da nota fiscal, realizamos a seguinte sequência: 1. Acessamos o sistema no menu Con</t>
+  </si>
+  <si>
+    <t>Baixa</t>
+  </si>
+  <si>
+    <t>Alex Julio Estacio</t>
+  </si>
+  <si>
+    <t>02/04/2026</t>
+  </si>
+  <si>
+    <t>11116111397</t>
+  </si>
+  <si>
+    <t>Altona || Conferência Entrada de Consignados - Melhoria</t>
+  </si>
+  <si>
+    <t>21/01/2026</t>
+  </si>
+  <si>
+    <t>11116094860</t>
+  </si>
+  <si>
+    <t>Centralização das aplicações de Retrabalho</t>
+  </si>
+  <si>
+    <t>35520</t>
+  </si>
+  <si>
+    <t>Aplicativo Tratamento Térmico - Bloco de Prova e Gráficos - Reunião</t>
+  </si>
+  <si>
+    <t>Bom dia, Estou fazendo a última verificação no novo sistema do Tratamento Térmico e vi que está faltando a parte de pesquisa de bloco de prova, conseguimos adicionar essa funcionalidade de pesquisa de bloco no novo sistema? Imagem da localização no menu onde é feita a pesquisa de blocos abaixo; Outr</t>
+  </si>
+  <si>
+    <t>Eduardo Basso Pinto</t>
+  </si>
+  <si>
+    <t>20/03/2026</t>
+  </si>
+  <si>
+    <t>11116115362</t>
+  </si>
+  <si>
+    <t>Alteração cadastro de materiais</t>
+  </si>
+  <si>
+    <t>11116112159</t>
+  </si>
+  <si>
+    <t>Sugestão FTFs</t>
+  </si>
+  <si>
+    <t>11116104413</t>
+  </si>
+  <si>
+    <t>Atualização da tela materiais endereçados</t>
+  </si>
+  <si>
+    <t>11116115595</t>
+  </si>
+  <si>
+    <t>SISTEMA INVOICE // NOVA ABA OBSERVAÇÕES PROFORMA</t>
+  </si>
+  <si>
+    <t>33130</t>
+  </si>
+  <si>
+    <t>Comercial</t>
+  </si>
+  <si>
+    <t>Novo Sistema</t>
+  </si>
+  <si>
+    <t>Identificar ID da oferta gerado no CRM</t>
+  </si>
+  <si>
     <t>N/A</t>
   </si>
   <si>
-    <t>Feito</t>
-  </si>
-  <si>
-    <t>Não</t>
-  </si>
-  <si>
-    <t>Semana 4</t>
-  </si>
-  <si>
-    <t>Janeiro</t>
-  </si>
-  <si>
-    <t>35754</t>
-  </si>
-  <si>
-    <t>Indicadores Diários - IROG</t>
-  </si>
-  <si>
-    <t>34599</t>
-  </si>
-  <si>
-    <t>Solicitação de serviço</t>
-  </si>
-  <si>
-    <t>Sistema de Embalagens - Relatório Requisição Embalagem por Sequência</t>
-  </si>
-  <si>
-    <t>Bom dia Sandro. Cristian me passou que o desenvolvimento do sistema para gestão de Embalagem está concluído. Ótima notícia. Desenvolver relatório conforme layout no anexo. Relatório será de período fechado de mês, após o fechamento do mês. Listar mesmo as requisições que não tenham vinculadas etique</t>
-  </si>
-  <si>
-    <t>Paulo Giovani da Cruz</t>
-  </si>
-  <si>
-    <t>Sistemas</t>
-  </si>
-  <si>
-    <t>35828</t>
-  </si>
-  <si>
-    <t>Romaneio</t>
-  </si>
-  <si>
-    <t>35974</t>
-  </si>
-  <si>
-    <t>Solicitação de atualização de integração no sistema de embalagens</t>
-  </si>
-  <si>
-    <t>35742</t>
-  </si>
-  <si>
-    <t>Melhoria do sistema de cadastro</t>
-  </si>
-  <si>
-    <t>32022</t>
-  </si>
-  <si>
-    <t>Projeto</t>
-  </si>
-  <si>
-    <t>Ajustes Dalca e Lianco</t>
-  </si>
-  <si>
-    <t>Boa tarde! Abrindo chamado referente ao desenvolvimento do sistema de apontamentos via CLP das células de rebarbação automatizadas. Atenciosamente,</t>
-  </si>
-  <si>
-    <t>Alta</t>
-  </si>
-  <si>
-    <t>Leonardo Barbosa de Moraes</t>
-  </si>
-  <si>
-    <t>09/03/2026</t>
-  </si>
-  <si>
-    <t>35814</t>
-  </si>
-  <si>
-    <t>Melhoria sistema de manutenção - Reunião</t>
-  </si>
-  <si>
-    <t>35353</t>
-  </si>
-  <si>
-    <t>Excelência Operacional</t>
-  </si>
-  <si>
-    <t>Criação do IROG do Tratamento Térmico</t>
-  </si>
-  <si>
-    <t>Bom dia Srs., Precisamos que seja criado uma aba para visualização do IROG do Tratamento Térmico. Incluir o ícone nessa aba: Link do apontamento do Tratamento Térmico: https://mes.altona.com.br/KB_EAA_TOTONETFrameworkOracle/wtt000.aspx Lançar os dados que estão sendo gerados nesse apontamento para a</t>
-  </si>
-  <si>
-    <t>Gabriel Lucas Kertichka</t>
-  </si>
-  <si>
-    <t>19/03/2026</t>
-  </si>
-  <si>
-    <t>33588</t>
-  </si>
-  <si>
-    <t>Indicador Cobertura de Estoques</t>
-  </si>
-  <si>
-    <t>35529</t>
-  </si>
-  <si>
-    <t>Log de método dentro do sistema de baixa de preventivas e planejamento e programação</t>
-  </si>
-  <si>
-    <t>35665</t>
-  </si>
-  <si>
-    <t>Fundição</t>
-  </si>
-  <si>
-    <t>APONTAMNETO LINHAS UPR - ADEQUAÇÕES PARA LINHA FHASE FOUR</t>
-  </si>
-  <si>
-    <t>Boa tarde, Adequações a serem feitas no sistema eletrônico UPR para linha Fhase Four. * Retirada da opção lado mesa A / B (não necessário, a linha não utiliza o sistema de mesa redonda). * Habilitar a opção de abrir parada sem sequência (habilitar essa função para todas as linhas). Obs; Durante os t</t>
-  </si>
-  <si>
-    <t>Douglas Garcia</t>
-  </si>
-  <si>
-    <t>01/06/2026</t>
-  </si>
-  <si>
-    <t>35550</t>
-  </si>
-  <si>
-    <t>Implementação de Índice de Qualidade de Manutenção</t>
-  </si>
-  <si>
-    <t>35367</t>
-  </si>
-  <si>
-    <t>Indicadores MTTR e MDT</t>
-  </si>
-  <si>
-    <t>Bom dia, Quero solicitar, se possível, fazer uma alteração no sistema de manutenção para que ele possa calcular o MTTR e o MDT separados. Todavia, sabendo que ambos se complementam porque o MDT calcula o tempo total da máquina parada que seria quando o operador abre a O.S e coloca a máquina em manut</t>
-  </si>
-  <si>
-    <t>Glória Danielly Lima Rodrigues</t>
-  </si>
-  <si>
-    <t>19/05/2026</t>
-  </si>
-  <si>
-    <t>35806</t>
-  </si>
-  <si>
-    <t>Correção</t>
-  </si>
-  <si>
-    <t>ALTERAÇÃO NA TELA DE LANÇAMENTO DE CTE</t>
-  </si>
-  <si>
-    <t>35729</t>
-  </si>
-  <si>
-    <t>Usinagem</t>
-  </si>
-  <si>
-    <t>Alteração aplicação Usinagem IROG</t>
-  </si>
-  <si>
-    <t>Boa tarde Felipe, Conforme conversamos via Teams, favor alterar base de dados para a aplicação Indicadores Usinagem, para a mesma base da Usinagem IROG ou abrir uma nova pasta na aplicação e criar os mesmos gráficos. Grato,</t>
-  </si>
-  <si>
-    <t>Caio Henrique Vicente Bento</t>
-  </si>
-  <si>
-    <t>27502</t>
-  </si>
-  <si>
-    <t>Cartão de Vazamento</t>
-  </si>
-  <si>
-    <t>35798</t>
-  </si>
-  <si>
-    <t>Melhorias sistema de corridas</t>
-  </si>
-  <si>
-    <t>35737</t>
-  </si>
-  <si>
-    <t>Correção Calculo MTBF</t>
-  </si>
-  <si>
-    <t>Homologação</t>
-  </si>
-  <si>
-    <t>Aberto</t>
-  </si>
-  <si>
-    <t>30012</t>
-  </si>
-  <si>
-    <t>Melhorias APS</t>
-  </si>
-  <si>
-    <t>Objetivo: alimentar dados mestres nas tabelas do APS 8-9. Levantamento de informações para a especificação funcional do projeto. ( TI especificação de interface inicial) REALIZADO @Edson João Hammermeister por favor indicar tempo para essa atividade. Atenciosamente, De: João Pedro Beccon Enviada em:</t>
-  </si>
-  <si>
-    <t>João Pedro Beccon</t>
-  </si>
-  <si>
-    <t>35755</t>
-  </si>
-  <si>
-    <t>Atalho Corridas</t>
-  </si>
-  <si>
-    <t>35751</t>
-  </si>
-  <si>
-    <t>SISTEMÁTICA REABERTURA DE ANÁLISE CRÍTICA</t>
-  </si>
-  <si>
-    <t>35250</t>
-  </si>
-  <si>
-    <t>Impressão de Solicitações</t>
-  </si>
-  <si>
-    <t>35808</t>
-  </si>
-  <si>
-    <t>Unificação de dados das aplicações de "Apontamento solda" x "Retrabalho Rebarbação</t>
-  </si>
-  <si>
-    <t>Bom dia! Percebi que não houve saída para abertura de um chamado sobre esta demanda "Unificação de dados das aplicações de "Apontamento solda" x "Retrabalho Rebarbação - item solda"" solicitada durante reuniões de meados de agosto e setembro/2025 conforme meus registros aqui. Solicito por aqui, entã</t>
-  </si>
-  <si>
-    <t>Fernanda da Costa Rodrigues</t>
-  </si>
-  <si>
-    <t>10/04/2026</t>
-  </si>
-  <si>
-    <t>34171</t>
-  </si>
-  <si>
-    <t>Contagem Proformas</t>
-  </si>
-  <si>
-    <t>35257</t>
-  </si>
-  <si>
-    <t>Integração do mapeamento digital com sistema do PCP</t>
-  </si>
-  <si>
-    <t>35908</t>
-  </si>
-  <si>
-    <t>Colocar campo de etiqueta no inventário</t>
-  </si>
-  <si>
-    <t>Implantação</t>
-  </si>
-  <si>
-    <t>35750</t>
-  </si>
-  <si>
-    <t>LOG DE ALTERAÇÃO DE CPP</t>
-  </si>
-  <si>
-    <t>35127</t>
-  </si>
-  <si>
-    <t>Altona || Estoque IMOB 39551 - Entradas + Consumo Diferente do Saldo</t>
-  </si>
-  <si>
-    <t>35430</t>
-  </si>
-  <si>
-    <t>FTF x Realizado</t>
-  </si>
-  <si>
-    <t>29853</t>
-  </si>
-  <si>
-    <t>WMS - Sistema de Picking - Distribuição de Estoque em carteira</t>
-  </si>
-  <si>
-    <t>Boa tarde Conforme conversamos, precisamos de um sistema dentro do WMS que faça a distribuição em tempo real do saldo do Estoque com a carteira. Conforme é realizado o faturamento, a carteira seja atualizada em tempo real, bem como a entrada e estorno do material. O sistema deve fornecer um relatóri</t>
-  </si>
-  <si>
-    <t>Djalma Machado</t>
-  </si>
-  <si>
-    <t>ADH</t>
-  </si>
-  <si>
-    <t>35631</t>
-  </si>
-  <si>
-    <t>Gestão de Pacotes - Ação Melhoria Sistema de Materiais x Supervisório</t>
-  </si>
-  <si>
-    <t>34779</t>
-  </si>
-  <si>
-    <t>ACESSO A TELA DE EXCLUSÃO DE SETOR EM VÁRIAS SEQUÊNCIAS</t>
-  </si>
-  <si>
-    <t>34848</t>
-  </si>
-  <si>
-    <t>Erro no cadastro do tempo padrão</t>
-  </si>
-  <si>
-    <t>36012</t>
-  </si>
-  <si>
-    <t>Incluir consistência para não permitir data/hora inicial em branco no apontamento</t>
-  </si>
-  <si>
-    <t>34720</t>
-  </si>
-  <si>
-    <t>Almoxarifado</t>
-  </si>
-  <si>
-    <t>Solicitação de Implementação – Coleta de Assinatura Digital para Declaração de Recebimento - Apresentação Sistema</t>
-  </si>
-  <si>
-    <t>Boa tarde Gostaria de solicitar a implementação de uma funcionalidade para coleta de assinatura digital referente à Declaração de Recebimento de materiais. Contexto do Processo Atual Hoje, ao receber o romaneio/cópia da nota fiscal, realizamos a seguinte sequência: 1. Acessamos o sistema no menu Con</t>
-  </si>
-  <si>
-    <t>Baixa</t>
-  </si>
-  <si>
-    <t>Alex Julio Estacio</t>
-  </si>
-  <si>
-    <t>02/04/2026</t>
-  </si>
-  <si>
-    <t>35128</t>
-  </si>
-  <si>
-    <t>Altona || Conferência Entrada de Consignados - Melhoria</t>
-  </si>
-  <si>
-    <t>Bom dia, Sandro! Dando continuidade ao processo de melhoria nas conferências do estoque peço que insiras no relatório abaixo: duas colunas conforme descrição abaixo e planilha anexa: 1) Finalidade (MP/C) - esse parâmetro servirá para conferir se um produto está classificado corretamente e consequent</t>
-  </si>
-  <si>
-    <t>Edson Vitor Scharf Filho</t>
-  </si>
-  <si>
-    <t>35791</t>
-  </si>
-  <si>
-    <t>Centralização das aplicações de Retrabalho</t>
-  </si>
-  <si>
-    <t>35520</t>
-  </si>
-  <si>
-    <t>Aplicativo Tratamento Térmico - Bloco de Prova e Gráficos - Reunião</t>
-  </si>
-  <si>
-    <t>Bom dia, Estou fazendo a última verificação no novo sistema do Tratamento Térmico e vi que está faltando a parte de pesquisa de bloco de prova, conseguimos adicionar essa funcionalidade de pesquisa de bloco no novo sistema? Imagem da localização no menu onde é feita a pesquisa de blocos abaixo; Outr</t>
-  </si>
-  <si>
-    <t>Eduardo Basso Pinto</t>
-  </si>
-  <si>
-    <t>20/03/2026</t>
-  </si>
-  <si>
-    <t>35765</t>
-  </si>
-  <si>
-    <t>Alteração cadastro de materiais</t>
-  </si>
-  <si>
-    <t>35766</t>
-  </si>
-  <si>
-    <t>Sugestão FTFs</t>
-  </si>
-  <si>
-    <t>35145</t>
-  </si>
-  <si>
-    <t>Atualização da tela materiais endereçados</t>
-  </si>
-  <si>
-    <t>35656</t>
-  </si>
-  <si>
-    <t>SISTEMA INVOICE // NOVA ABA OBSERVAÇÕES PROFORMA</t>
-  </si>
-  <si>
-    <t>33130</t>
-  </si>
-  <si>
-    <t>Comercial</t>
-  </si>
-  <si>
-    <t>Novo Sistema</t>
-  </si>
-  <si>
-    <t>Identificar ID da oferta gerado no CRM</t>
-  </si>
-  <si>
     <t>Laura Herrmann Schmickler</t>
   </si>
   <si>
     <t>Conferência do envio em massa e correção de registros não enviados</t>
   </si>
   <si>
-    <t>35779</t>
+    <t>11116104689</t>
   </si>
   <si>
     <t>Chamado alteração máquina</t>
   </si>
   <si>
-    <t>35417</t>
-  </si>
-  <si>
-    <t>Engenharia</t>
+    <t>11116104591</t>
   </si>
   <si>
     <t>MRP NO SETOR DE PRÉ-ANÁLISE (516)</t>
   </si>
   <si>
-    <t>Bom dia, Favor criar um formulário no setor 516 que possibilite a inclusão de informações no MRP do CPP, da mesma forma que existe no setor 509/527. Favor criar trava de movimentação do setor até que o formulário esteja respondido, portanto incluir opção de "SIM" ou "NÃO" antes do grid (Há necessida</t>
-  </si>
-  <si>
-    <t>Willian Gabriel Paixão dos Santos</t>
-  </si>
-  <si>
-    <t>06/03/2026</t>
-  </si>
-  <si>
     <t>32150</t>
   </si>
   <si>
@@ -561,6 +564,9 @@
     <t>35769</t>
   </si>
   <si>
+    <t>Logistica</t>
+  </si>
+  <si>
     <t>Inclusão de sequencia de conjunto</t>
   </si>
   <si>
@@ -576,7 +582,7 @@
     <t>Período</t>
   </si>
   <si>
-    <t>SPRINT 2026-05</t>
+    <t>Jan/2026</t>
   </si>
   <si>
     <t>Base</t>
@@ -625,9 +631,6 @@
   </si>
   <si>
     <t>Muito Alta</t>
-  </si>
-  <si>
-    <t>Sim</t>
   </si>
   <si>
     <t>Semana 1</t>
@@ -1224,7 +1227,7 @@
         <v>23</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>25</v>
@@ -1241,7 +1244,7 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>16</v>
@@ -1250,22 +1253,22 @@
         <v>17</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>23</v>
@@ -1288,7 +1291,7 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>16</v>
@@ -1300,10 +1303,10 @@
         <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>20</v>
@@ -1335,7 +1338,7 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>16</v>
@@ -1347,10 +1350,10 @@
         <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>20</v>
@@ -1365,7 +1368,7 @@
         <v>23</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>25</v>
@@ -1382,7 +1385,7 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>16</v>
@@ -1394,10 +1397,10 @@
         <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>20</v>
@@ -1412,7 +1415,7 @@
         <v>23</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>25</v>
@@ -1429,37 +1432,37 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>47</v>
-      </c>
       <c r="H8" s="2" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>25</v>
@@ -1476,7 +1479,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>16</v>
@@ -1488,10 +1491,10 @@
         <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>20</v>
@@ -1523,43 +1526,43 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="G10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H10" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="I10" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="J10" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K10" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="G10" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H10" s="2" t="s">
+      <c r="L10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M10" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>26</v>
       </c>
       <c r="N10" s="2" t="s">
         <v>27</v>
@@ -1570,7 +1573,7 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>16</v>
@@ -1582,13 +1585,13 @@
         <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>21</v>
@@ -1600,7 +1603,7 @@
         <v>23</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>25</v>
@@ -1617,7 +1620,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>16</v>
@@ -1629,10 +1632,10 @@
         <v>18</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>20</v>
@@ -1664,43 +1667,43 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="C13" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="G13" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H13" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="G13" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H13" s="2" t="s">
+      <c r="I13" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K13" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="I13" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>67</v>
-      </c>
       <c r="L13" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="N13" s="2" t="s">
         <v>27</v>
@@ -1711,7 +1714,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>16</v>
@@ -1723,10 +1726,10 @@
         <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>20</v>
@@ -1758,16 +1761,16 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="C15" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>71</v>
@@ -1782,7 +1785,7 @@
         <v>73</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>23</v>
@@ -1794,7 +1797,7 @@
         <v>25</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="N15" s="2" t="s">
         <v>27</v>
@@ -1835,7 +1838,7 @@
         <v>23</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>25</v>
@@ -1852,31 +1855,31 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>23</v>
@@ -1888,7 +1891,7 @@
         <v>25</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="N17" s="2" t="s">
         <v>27</v>
@@ -1899,7 +1902,7 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>16</v>
@@ -1911,10 +1914,10 @@
         <v>18</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>20</v>
@@ -1929,7 +1932,7 @@
         <v>23</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>24</v>
+        <v>86</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>25</v>
@@ -1946,7 +1949,7 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>16</v>
@@ -1958,10 +1961,10 @@
         <v>18</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>20</v>
@@ -1993,7 +1996,7 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>16</v>
@@ -2005,10 +2008,10 @@
         <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>20</v>
@@ -2023,13 +2026,13 @@
         <v>23</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>24</v>
+        <v>91</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>90</v>
+        <v>56</v>
       </c>
       <c r="N20" s="2" t="s">
         <v>27</v>
@@ -2040,31 +2043,31 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>23</v>
@@ -2076,7 +2079,7 @@
         <v>25</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="N21" s="2" t="s">
         <v>27</v>
@@ -2087,7 +2090,7 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>16</v>
@@ -2099,10 +2102,10 @@
         <v>18</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>20</v>
@@ -2134,7 +2137,7 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>16</v>
@@ -2146,10 +2149,10 @@
         <v>18</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>20</v>
@@ -2164,7 +2167,7 @@
         <v>23</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>24</v>
+        <v>102</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>25</v>
@@ -2181,7 +2184,7 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>16</v>
@@ -2193,10 +2196,10 @@
         <v>18</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>20</v>
@@ -2211,7 +2214,7 @@
         <v>23</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>25</v>
@@ -2228,7 +2231,7 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>16</v>
@@ -2237,34 +2240,34 @@
         <v>17</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>90</v>
+        <v>56</v>
       </c>
       <c r="N25" s="2" t="s">
         <v>27</v>
@@ -2275,7 +2278,7 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>16</v>
@@ -2287,10 +2290,10 @@
         <v>18</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>20</v>
@@ -2322,7 +2325,7 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>16</v>
@@ -2334,10 +2337,10 @@
         <v>18</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>20</v>
@@ -2369,7 +2372,7 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>16</v>
@@ -2381,10 +2384,10 @@
         <v>18</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>20</v>
@@ -2399,10 +2402,10 @@
         <v>23</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>24</v>
+        <v>91</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="M28" s="2" t="s">
         <v>26</v>
@@ -2416,7 +2419,7 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>16</v>
@@ -2428,10 +2431,10 @@
         <v>18</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>20</v>
@@ -2463,7 +2466,7 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>16</v>
@@ -2475,10 +2478,10 @@
         <v>18</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>20</v>
@@ -2510,7 +2513,7 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>16</v>
@@ -2522,10 +2525,10 @@
         <v>18</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>20</v>
@@ -2540,7 +2543,7 @@
         <v>23</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>24</v>
+        <v>102</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>25</v>
@@ -2557,31 +2560,31 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>16</v>
+        <v>124</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="J32" s="2" t="s">
         <v>23</v>
@@ -2593,7 +2596,7 @@
         <v>25</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="N32" s="2" t="s">
         <v>27</v>
@@ -2604,7 +2607,7 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>16</v>
@@ -2616,13 +2619,13 @@
         <v>18</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>21</v>
@@ -2651,7 +2654,7 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>16</v>
@@ -2663,10 +2666,10 @@
         <v>18</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>20</v>
@@ -2698,7 +2701,7 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>16</v>
@@ -2710,10 +2713,10 @@
         <v>18</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>20</v>
@@ -2728,7 +2731,7 @@
         <v>23</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>24</v>
+        <v>102</v>
       </c>
       <c r="L35" s="2" t="s">
         <v>25</v>
@@ -2745,7 +2748,7 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>16</v>
@@ -2757,10 +2760,10 @@
         <v>18</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>20</v>
@@ -2792,43 +2795,43 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="J37" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="L37" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="N37" s="2" t="s">
         <v>27</v>
@@ -2839,7 +2842,7 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>16</v>
@@ -2848,28 +2851,28 @@
         <v>17</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>142</v>
+        <v>21</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>123</v>
+        <v>22</v>
       </c>
       <c r="J38" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>49</v>
+        <v>146</v>
       </c>
       <c r="L38" s="2" t="s">
         <v>25</v>
@@ -2886,7 +2889,7 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>16</v>
@@ -2898,10 +2901,10 @@
         <v>18</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>20</v>
@@ -2916,7 +2919,7 @@
         <v>23</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L39" s="2" t="s">
         <v>25</v>
@@ -2933,43 +2936,43 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>16</v>
+        <v>62</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="J40" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="L40" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="N40" s="2" t="s">
         <v>27</v>
@@ -2980,7 +2983,7 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>16</v>
@@ -2992,10 +2995,10 @@
         <v>18</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>20</v>
@@ -3027,7 +3030,7 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>16</v>
@@ -3039,10 +3042,10 @@
         <v>18</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>20</v>
@@ -3074,7 +3077,7 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>16</v>
@@ -3086,10 +3089,10 @@
         <v>18</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>20</v>
@@ -3121,7 +3124,7 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>16</v>
@@ -3133,10 +3136,10 @@
         <v>18</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>20</v>
@@ -3168,37 +3171,37 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>24</v>
+        <v>166</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="J45" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L45" s="2" t="s">
         <v>25</v>
@@ -3215,37 +3218,37 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>24</v>
+        <v>166</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="J46" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L46" s="2" t="s">
         <v>25</v>
@@ -3262,7 +3265,7 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>16</v>
@@ -3274,10 +3277,10 @@
         <v>18</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>20</v>
@@ -3292,7 +3295,7 @@
         <v>23</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>24</v>
+        <v>102</v>
       </c>
       <c r="L47" s="2" t="s">
         <v>25</v>
@@ -3309,37 +3312,37 @@
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>167</v>
+        <v>16</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>170</v>
+        <v>21</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>123</v>
+        <v>22</v>
       </c>
       <c r="J48" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>171</v>
+        <v>38</v>
       </c>
       <c r="L48" s="2" t="s">
         <v>25</v>
@@ -3356,31 +3359,31 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>16</v>
+        <v>124</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="J49" s="2" t="s">
         <v>23</v>
@@ -3389,10 +3392,10 @@
         <v>74</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="N49" s="2" t="s">
         <v>27</v>
@@ -3403,31 +3406,31 @@
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>16</v>
+        <v>124</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="J50" s="2" t="s">
         <v>23</v>
@@ -3436,10 +3439,10 @@
         <v>74</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>90</v>
+        <v>56</v>
       </c>
       <c r="N50" s="2" t="s">
         <v>27</v>
@@ -3450,43 +3453,43 @@
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>16</v>
+        <v>124</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="J51" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="N51" s="2" t="s">
         <v>27</v>
@@ -3497,40 +3500,40 @@
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>16</v>
+        <v>183</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>76</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="J52" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>24</v>
+        <v>91</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="M52" s="2" t="s">
         <v>26</v>
@@ -3555,23 +3558,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -3579,16 +3582,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -3596,18 +3599,18 @@
         <v>51</v>
       </c>
       <c r="D5" s="5">
-        <v>0</v>
+        <v>0.7450980392156863</v>
       </c>
       <c r="G5" s="4">
-        <v>78.85</v>
+        <v>9.67</v>
       </c>
       <c r="J5" s="4">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -3620,7 +3623,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="K23">
         <v>4</v>
@@ -3628,7 +3631,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -3659,12 +3662,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B2">
         <v>51</v>
@@ -3672,41 +3675,41 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>0</v>
+        <v>0.7450980392156863</v>
       </c>
       <c r="B5" s="7"/>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>78.85</v>
+        <v>9.67</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -3714,7 +3717,7 @@
         <v>16</v>
       </c>
       <c r="B10">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="D10" t="s">
         <v>17</v>
@@ -3723,16 +3726,16 @@
         <v>43</v>
       </c>
       <c r="G10" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>204</v>
+        <v>26</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="M10" t="s">
         <v>25</v>
@@ -3741,18 +3744,18 @@
         <v>44</v>
       </c>
       <c r="P10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q10">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>159</v>
+        <v>124</v>
       </c>
       <c r="B11">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D11" t="s">
         <v>76</v>
@@ -3761,39 +3764,39 @@
         <v>4</v>
       </c>
       <c r="G11" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H11">
         <v>8</v>
       </c>
       <c r="J11" t="s">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="K11">
-        <v>48</v>
+        <v>13</v>
       </c>
       <c r="M11" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="N11">
         <v>0</v>
       </c>
       <c r="P11" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q11">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="B12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -3805,45 +3808,45 @@
         <v>42</v>
       </c>
       <c r="J12" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N12">
         <v>0</v>
       </c>
       <c r="P12" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q12">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>63</v>
+        <v>163</v>
       </c>
       <c r="B13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="E13">
         <v>2</v>
       </c>
       <c r="G13" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="H13">
         <v>1</v>
       </c>
       <c r="M13" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="N13">
         <v>0</v>
@@ -3852,24 +3855,24 @@
         <v>27</v>
       </c>
       <c r="Q13">
-        <v>35</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>79</v>
+        <v>49</v>
       </c>
       <c r="B14">
         <v>1</v>
       </c>
       <c r="G14" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="M14" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="N14">
         <v>4</v>
@@ -3877,13 +3880,13 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>133</v>
+        <v>70</v>
       </c>
       <c r="B15">
         <v>1</v>
       </c>
       <c r="M15" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="N15">
         <v>3</v>
@@ -3891,32 +3894,52 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>167</v>
+        <v>80</v>
       </c>
       <c r="B16">
         <v>1</v>
       </c>
       <c r="M16" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N16">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="13:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>94</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
       <c r="M17" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N17">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>138</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>183</v>
+      </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
       <c r="D19" s="6" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
         <v>0</v>
       </c>
@@ -3924,7 +3947,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -3932,142 +3955,142 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>62</v>
+        <v>89</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>63</v>
+        <v>16</v>
       </c>
       <c r="F21" s="2">
-        <v>110</v>
+        <v>127</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>70</v>
+        <v>105</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F22" s="2">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>71</v>
+        <v>106</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>78</v>
+        <v>176</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="F23" s="2">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>80</v>
+        <v>177</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>91</v>
+        <v>61</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>16</v>
+        <v>62</v>
       </c>
       <c r="F24" s="2">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>92</v>
+        <v>63</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>119</v>
+        <v>69</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="F25" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>120</v>
+        <v>71</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>172</v>
+        <v>79</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>16</v>
+        <v>80</v>
       </c>
       <c r="F26" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>173</v>
+        <v>81</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>132</v>
+        <v>93</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>133</v>
+        <v>94</v>
       </c>
       <c r="F27" s="2">
-        <v>50</v>
+        <v>99</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>134</v>
+        <v>95</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>145</v>
+        <v>123</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>16</v>
+        <v>124</v>
       </c>
       <c r="F28" s="2">
-        <v>37</v>
+        <v>99</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>146</v>
+        <v>125</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>16</v>
+        <v>124</v>
       </c>
       <c r="F29" s="2">
-        <v>37</v>
+        <v>99</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="F30" s="2">
         <v>52</v>
       </c>
-      <c r="E30" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F30" s="2">
-        <v>36</v>
-      </c>
       <c r="G30" s="2" t="s">
-        <v>54</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
